--- a/data/quotas/quota_onnuri_서울_송파구_풍납시장_온누리쿼터_검증_1791809677890.xlsx
+++ b/data/quotas/quota_onnuri_서울_송파구_풍납시장_온누리쿼터_검증_1791809677890.xlsx
@@ -397,22 +397,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P4"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.43359375" customWidth="1"/>
     <col min="4" max="4" width="19.234375" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.43359375" customWidth="1"/>
-    <col min="9" max="9" width="17.03515625" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="45.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21.43359375" customWidth="1"/>
     <col min="11" max="11" width="17.03515625" customWidth="1"/>
     <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="13" max="13" width="17.03515625" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.6328125" customWidth="1"/>
+    <col min="16" max="16" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,30 +434,36 @@
         <v>대표자명</v>
       </c>
       <c r="F1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="G1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="H1" t="str">
         <v>주소</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>온누리업종</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>마켓비즈산업분류</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>개업/설립일</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>온누리지류</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>온누리디지털</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>전화번호</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>가맹상태</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>기업규모</v>
       </c>
     </row>
@@ -476,30 +484,36 @@
         <v>연락처</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>수산물</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>신선</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>2020.10.06</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Y</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>N</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>정상가맹</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>소상공인</v>
       </c>
     </row>
@@ -520,30 +534,36 @@
         <v>연락처</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>서울특별시 송파구 풍납동 87-4 예작헤어라인</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>두발 미용업</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>2012.03.13</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>Y</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>Y</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>정상가맹</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>소상공인</v>
       </c>
     </row>
@@ -564,36 +584,42 @@
         <v>연락처</v>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>서울특별시 송파구 풍납동 2층 201호</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>피부 미용업</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>2023.10.06</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>Y</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>N</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>정상가맹</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>소상공인</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>